--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9182,0.0202,0.0433,0.0009</t>
-  </si>
-  <si>
-    <t>0.8446,0.0236,0.0337,0.0237</t>
-  </si>
-  <si>
-    <t>0.8972,0.0242,0.0547,0.0024</t>
-  </si>
-  <si>
-    <t>0.8515,0.0786,0.0339,0.0034</t>
-  </si>
-  <si>
-    <t>0.6879,0.0704,0.0309,0.0457</t>
-  </si>
-  <si>
-    <t>0.7111,0.1019,0.0480,0.0423</t>
-  </si>
-  <si>
-    <t>0.7613,0.0683,0.0744,0.0228</t>
-  </si>
-  <si>
-    <t>0.6323,0.1139,0.0472,0.0438</t>
-  </si>
-  <si>
-    <t>0.8162,0.0736,0.0316,0.0130</t>
-  </si>
-  <si>
-    <t>0.8626,0.0599,0.0175,0.0073</t>
-  </si>
-  <si>
-    <t>0.7813,0.0961,0.0466,0.0137</t>
-  </si>
-  <si>
-    <t>0.6051,0.2202,0.0627,0.0238</t>
-  </si>
-  <si>
-    <t>0.9199,0.0236,0.0538,0.0003</t>
-  </si>
-  <si>
-    <t>0.9598,0.0107,0.0214,0.0002</t>
-  </si>
-  <si>
-    <t>0.9603,0.0167,0.0156,0.0005</t>
-  </si>
-  <si>
-    <t>0.9431,0.0123,0.0371,0.0004</t>
-  </si>
-  <si>
-    <t>0.8238,0.1376,0.0765,0.0031</t>
-  </si>
-  <si>
-    <t>0.6991,0.3925,0.0427,0.0008</t>
-  </si>
-  <si>
-    <t>0.4659,0.6115,0.0867,0.0021</t>
-  </si>
-  <si>
-    <t>0.7549,0.1302,0.1036,0.0058</t>
-  </si>
-  <si>
-    <t>0.0998,0.9218,0.0732,0.0012</t>
-  </si>
-  <si>
-    <t>0.0838,0.9415,0.0448,0.0007</t>
-  </si>
-  <si>
-    <t>0.9588,0.0075,0.0212,0.0004</t>
-  </si>
-  <si>
-    <t>0.9390,0.0263,0.0254,0.0005</t>
-  </si>
-  <si>
-    <t>0.9056,0.0072,0.0882,0.0003</t>
-  </si>
-  <si>
-    <t>0.9383,0.0084,0.0456,0.0004</t>
-  </si>
-  <si>
-    <t>0.9759,0.0030,0.0156,0.0001</t>
-  </si>
-  <si>
-    <t>0.8864,0.0159,0.1310,0.0005</t>
-  </si>
-  <si>
-    <t>0.9235,0.0047,0.0694,0.0004</t>
-  </si>
-  <si>
-    <t>0.5370,0.4526,0.1206,0.0023</t>
-  </si>
-  <si>
-    <t>0.8170,0.1235,0.0874,0.0013</t>
-  </si>
-  <si>
-    <t>0.1400,0.3000,0.7870,0.0020</t>
-  </si>
-  <si>
-    <t>0.7893,0.1507,0.0751,0.0020</t>
-  </si>
-  <si>
-    <t>0.8355,0.1364,0.0305,0.0022</t>
-  </si>
-  <si>
-    <t>0.7636,0.1975,0.0476,0.0079</t>
-  </si>
-  <si>
-    <t>0.7891,0.1026,0.0797,0.0063</t>
-  </si>
-  <si>
-    <t>0.8689,0.1159,0.0445,0.0019</t>
-  </si>
-  <si>
-    <t>0.4671,0.1905,0.2763,0.0034</t>
-  </si>
-  <si>
-    <t>0.9583,0.0019,0.0381,0.0002</t>
-  </si>
-  <si>
-    <t>0.9642,0.0020,0.0462,0.0001</t>
-  </si>
-  <si>
-    <t>0.9854,0.0006,0.0113,0.0000</t>
-  </si>
-  <si>
-    <t>0.9757,0.0034,0.0207,0.0000</t>
-  </si>
-  <si>
-    <t>0.6388,0.3828,0.0348,0.0005</t>
-  </si>
-  <si>
-    <t>0.8875,0.0079,0.1559,0.0002</t>
-  </si>
-  <si>
-    <t>0.9456,0.0226,0.0126,0.0013</t>
-  </si>
-  <si>
-    <t>0.6147,0.4756,0.0612,0.0012</t>
-  </si>
-  <si>
-    <t>0.4236,0.7250,0.0390,0.0007</t>
-  </si>
-  <si>
-    <t>0.5949,0.4285,0.1145,0.0004</t>
-  </si>
-  <si>
-    <t>0.6258,0.0185,0.4190,0.0005</t>
-  </si>
-  <si>
-    <t>0.5495,0.0087,0.7046,0.0003</t>
-  </si>
-  <si>
-    <t>0.9619,0.0096,0.0242,0.0001</t>
-  </si>
-  <si>
-    <t>0.7180,0.0064,0.4467,0.0001</t>
-  </si>
-  <si>
-    <t>0.7245,0.0034,0.4461,0.0002</t>
-  </si>
-  <si>
-    <t>0.7770,0.0032,0.3864,0.0001</t>
-  </si>
-  <si>
-    <t>0.8495,0.0613,0.0242,0.0078</t>
-  </si>
-  <si>
-    <t>0.7940,0.1090,0.0492,0.0107</t>
-  </si>
-  <si>
-    <t>0.4238,0.5553,0.0830,0.0080</t>
-  </si>
-  <si>
-    <t>0.0930,0.2387,0.9147,0.0029</t>
-  </si>
-  <si>
-    <t>0.7053,0.1495,0.0648,0.0183</t>
-  </si>
-  <si>
-    <t>0.7306,0.1237,0.0558,0.0217</t>
-  </si>
-  <si>
-    <t>0.8711,0.0433,0.0332,0.0073</t>
-  </si>
-  <si>
-    <t>0.5439,0.0366,0.4881,0.0003</t>
-  </si>
-  <si>
-    <t>0.7051,0.0058,0.4849,0.0003</t>
-  </si>
-  <si>
-    <t>0.8040,0.0071,0.2429,0.0003</t>
-  </si>
-  <si>
-    <t>0.7744,0.0312,0.2431,0.0004</t>
-  </si>
-  <si>
-    <t>0.5411,0.0016,0.7459,0.0003</t>
-  </si>
-  <si>
-    <t>0.8090,0.2647,0.0199,0.0007</t>
-  </si>
-  <si>
-    <t>0.0047,0.9962,0.0154,0.0001</t>
-  </si>
-  <si>
-    <t>0.9222,0.0310,0.0381,0.0014</t>
-  </si>
-  <si>
-    <t>0.9096,0.0411,0.0343,0.0013</t>
-  </si>
-  <si>
-    <t>0.2837,0.1952,0.7239,0.0054</t>
-  </si>
-  <si>
-    <t>0.7336,0.0266,0.3255,0.0003</t>
-  </si>
-  <si>
-    <t>0.8981,0.0445,0.0307,0.0000</t>
-  </si>
-  <si>
-    <t>0.8114,0.2762,0.0040,0.0000</t>
-  </si>
-  <si>
-    <t>0.9021,0.0061,0.1388,0.0001</t>
-  </si>
-  <si>
-    <t>0.9372,0.0283,0.0231,0.0016</t>
-  </si>
-  <si>
-    <t>0.8800,0.0613,0.0308,0.0027</t>
-  </si>
-  <si>
-    <t>0.9539,0.0208,0.0113,0.0014</t>
-  </si>
-  <si>
-    <t>0.9455,0.0196,0.0191,0.0013</t>
-  </si>
-  <si>
-    <t>0.8942,0.0215,0.0205,0.0097</t>
-  </si>
-  <si>
-    <t>0.9527,0.0147,0.0195,0.0011</t>
-  </si>
-  <si>
-    <t>0.7195,0.2920,0.0575,0.0004</t>
-  </si>
-  <si>
-    <t>0.6496,0.0383,0.3291,0.0003</t>
-  </si>
-  <si>
-    <t>0.8438,0.0089,0.1634,0.0001</t>
-  </si>
-  <si>
-    <t>0.9295,0.0013,0.1003,0.0001</t>
-  </si>
-  <si>
-    <t>0.4774,0.1943,0.2674,0.0003</t>
-  </si>
-  <si>
-    <t>0.9174,0.0178,0.0568,0.0001</t>
-  </si>
-  <si>
-    <t>0.6198,0.1403,0.0461,0.0297</t>
-  </si>
-  <si>
-    <t>0.7795,0.0770,0.0631,0.0228</t>
-  </si>
-  <si>
-    <t>0.7065,0.1866,0.1194,0.0092</t>
-  </si>
-  <si>
-    <t>0.7393,0.0861,0.0914,0.0437</t>
-  </si>
-  <si>
-    <t>0.7222,0.1433,0.0535,0.0118</t>
-  </si>
-  <si>
-    <t>0.8760,0.0378,0.0178,0.0108</t>
-  </si>
-  <si>
-    <t>0.6627,0.0934,0.0611,0.0410</t>
-  </si>
-  <si>
-    <t>0.7377,0.0677,0.0514,0.0405</t>
-  </si>
-  <si>
-    <t>0.9083,0.0305,0.0174,0.0056</t>
-  </si>
-  <si>
-    <t>0.5653,0.3141,0.0761,0.0142</t>
-  </si>
-  <si>
-    <t>0.7911,0.1080,0.0531,0.0070</t>
-  </si>
-  <si>
-    <t>0.8681,0.0326,0.0370,0.0098</t>
-  </si>
-  <si>
-    <t>0.6370,0.1130,0.0731,0.0453</t>
-  </si>
-  <si>
-    <t>0.8184,0.0573,0.0391,0.0170</t>
-  </si>
-  <si>
-    <t>0.6991,0.0970,0.0473,0.0305</t>
-  </si>
-  <si>
-    <t>0.8187,0.0514,0.0295,0.0180</t>
-  </si>
-  <si>
-    <t>0.4058,0.0070,0.7954,0.0003</t>
-  </si>
-  <si>
-    <t>0.9201,0.0078,0.0737,0.0005</t>
-  </si>
-  <si>
-    <t>0.9782,0.0037,0.0127,0.0001</t>
-  </si>
-  <si>
-    <t>0.9595,0.0087,0.0245,0.0002</t>
-  </si>
-  <si>
-    <t>0.3082,0.7446,0.1044,0.0035</t>
-  </si>
-  <si>
-    <t>0.8263,0.1076,0.0941,0.0012</t>
-  </si>
-  <si>
-    <t>0.4403,0.5644,0.1339,0.0063</t>
-  </si>
-  <si>
-    <t>0.6664,0.2698,0.0686,0.0053</t>
-  </si>
-  <si>
-    <t>0.3799,0.6364,0.1464,0.0020</t>
-  </si>
-  <si>
-    <t>0.3194,0.7719,0.0489,0.0023</t>
-  </si>
-  <si>
-    <t>0.7596,0.1494,0.0928,0.0076</t>
-  </si>
-  <si>
-    <t>0.9201,0.0541,0.0176,0.0010</t>
-  </si>
-  <si>
-    <t>0.9310,0.0141,0.0501,0.0004</t>
-  </si>
-  <si>
-    <t>0.9561,0.0163,0.0132,0.0004</t>
-  </si>
-  <si>
-    <t>0.9235,0.0264,0.0352,0.0014</t>
-  </si>
-  <si>
-    <t>0.9325,0.0206,0.0312,0.0006</t>
-  </si>
-  <si>
-    <t>0.7416,0.3210,0.0472,0.0004</t>
-  </si>
-  <si>
-    <t>0.9067,0.0956,0.0230,0.0005</t>
-  </si>
-  <si>
-    <t>0.9504,0.0218,0.0175,0.0006</t>
-  </si>
-  <si>
-    <t>0.0543,0.9287,0.3058,0.0026</t>
-  </si>
-  <si>
-    <t>0.8927,0.0698,0.0362,0.0005</t>
-  </si>
-  <si>
-    <t>0.8318,0.0908,0.0651,0.0048</t>
-  </si>
-  <si>
-    <t>0.7611,0.1408,0.1122,0.0058</t>
-  </si>
-  <si>
-    <t>0.9039,0.0299,0.0134,0.0054</t>
-  </si>
-  <si>
-    <t>0.8838,0.0283,0.0302,0.0097</t>
-  </si>
-  <si>
-    <t>0.7789,0.1047,0.0404,0.0116</t>
-  </si>
-  <si>
-    <t>0.7511,0.1481,0.0464,0.0063</t>
-  </si>
-  <si>
-    <t>0.8272,0.0550,0.0611,0.0087</t>
-  </si>
-  <si>
-    <t>0.7290,0.1087,0.1464,0.0117</t>
-  </si>
-  <si>
-    <t>0.8276,0.0953,0.0259,0.0086</t>
-  </si>
-  <si>
-    <t>0.7828,0.0552,0.0658,0.0216</t>
-  </si>
-  <si>
-    <t>0.6640,0.1280,0.1634,0.0004</t>
-  </si>
-  <si>
-    <t>0.9836,0.0029,0.0090,0.0000</t>
-  </si>
-  <si>
-    <t>0.6940,0.0076,0.4732,0.0004</t>
-  </si>
-  <si>
-    <t>0.7683,0.0121,0.3574,0.0008</t>
-  </si>
-  <si>
-    <t>0.9027,0.0567,0.0418,0.0022</t>
-  </si>
-  <si>
-    <t>0.9249,0.0314,0.0454,0.0005</t>
-  </si>
-  <si>
-    <t>0.9078,0.0244,0.0618,0.0004</t>
-  </si>
-  <si>
-    <t>0.8854,0.0406,0.0325,0.0030</t>
-  </si>
-  <si>
-    <t>0.8945,0.0356,0.0630,0.0007</t>
-  </si>
-  <si>
-    <t>0.8575,0.0255,0.0071,0.0186</t>
-  </si>
-  <si>
-    <t>0.9469,0.0217,0.0091,0.0017</t>
-  </si>
-  <si>
-    <t>0.8936,0.0575,0.0275,0.0029</t>
-  </si>
-  <si>
-    <t>0.3878,0.2378,0.3756,0.0010</t>
-  </si>
-  <si>
-    <t>0.7251,0.1230,0.0562,0.0190</t>
-  </si>
-  <si>
-    <t>0.8559,0.0889,0.0422,0.0037</t>
-  </si>
-  <si>
-    <t>0.7669,0.0832,0.0743,0.0154</t>
-  </si>
-  <si>
-    <t>0.7904,0.1675,0.0789,0.0026</t>
-  </si>
-  <si>
-    <t>0.8913,0.0456,0.0520,0.0011</t>
-  </si>
-  <si>
-    <t>0.7988,0.1092,0.0231,0.0075</t>
-  </si>
-  <si>
-    <t>0.6854,0.1328,0.0865,0.0226</t>
-  </si>
-  <si>
-    <t>0.3558,0.1767,0.5636,0.0055</t>
-  </si>
-  <si>
-    <t>0.8595,0.0482,0.0323,0.0091</t>
-  </si>
-  <si>
-    <t>0.7838,0.1485,0.0615,0.0087</t>
-  </si>
-  <si>
-    <t>0.8843,0.0749,0.0383,0.0018</t>
-  </si>
-  <si>
-    <t>0.8876,0.0390,0.0374,0.0024</t>
-  </si>
-  <si>
-    <t>0.8479,0.1177,0.0479,0.0015</t>
-  </si>
-  <si>
-    <t>0.7134,0.2875,0.0865,0.0028</t>
-  </si>
-  <si>
-    <t>0.8760,0.0516,0.0428,0.0032</t>
-  </si>
-  <si>
-    <t>0.8904,0.0319,0.0218,0.0065</t>
-  </si>
-  <si>
-    <t>0.7974,0.0699,0.0253,0.0180</t>
-  </si>
-  <si>
-    <t>0.7782,0.1302,0.0314,0.0128</t>
-  </si>
-  <si>
-    <t>0.7622,0.0814,0.0259,0.0186</t>
-  </si>
-  <si>
-    <t>0.7749,0.0667,0.0369,0.0292</t>
-  </si>
-  <si>
-    <t>0.8302,0.0496,0.0317,0.0158</t>
-  </si>
-  <si>
-    <t>0.7708,0.0744,0.0714,0.0225</t>
-  </si>
-  <si>
-    <t>0.8416,0.0808,0.0437,0.0048</t>
-  </si>
-  <si>
-    <t>0.6474,0.0525,0.0422,0.0942</t>
-  </si>
-  <si>
-    <t>0.7300,0.1710,0.0803,0.0057</t>
-  </si>
-  <si>
-    <t>0.7270,0.1565,0.0966,0.0104</t>
-  </si>
-  <si>
-    <t>0.7140,0.1604,0.0583,0.0104</t>
-  </si>
-  <si>
-    <t>0.9047,0.0223,0.0106,0.0058</t>
-  </si>
-  <si>
-    <t>0.7658,0.1605,0.0545,0.0082</t>
-  </si>
-  <si>
-    <t>0.8010,0.0973,0.0470,0.0068</t>
-  </si>
-  <si>
-    <t>0.8176,0.0867,0.0419,0.0069</t>
-  </si>
-  <si>
-    <t>0.7762,0.1546,0.0370,0.0053</t>
-  </si>
-  <si>
-    <t>0.1032,0.0204,0.9647,0.0002</t>
-  </si>
-  <si>
-    <t>0.7747,0.1305,0.0722,0.0051</t>
-  </si>
-  <si>
-    <t>0.7552,0.0088,0.3445,0.0017</t>
-  </si>
-  <si>
-    <t>0.8996,0.0077,0.1323,0.0003</t>
-  </si>
-  <si>
-    <t>0.7167,0.0287,0.3920,0.0008</t>
-  </si>
-  <si>
-    <t>0.1086,0.2385,0.8676,0.0035</t>
-  </si>
-  <si>
-    <t>0.9435,0.0051,0.0563,0.0002</t>
-  </si>
-  <si>
-    <t>0.6609,0.0102,0.5709,0.0007</t>
-  </si>
-  <si>
-    <t>0.8567,0.0104,0.1508,0.0001</t>
-  </si>
-  <si>
-    <t>0.9246,0.0172,0.0616,0.0003</t>
-  </si>
-  <si>
-    <t>0.8801,0.0337,0.0862,0.0004</t>
-  </si>
-  <si>
-    <t>0.9256,0.0241,0.0297,0.0007</t>
-  </si>
-  <si>
-    <t>0.8523,0.0783,0.0756,0.0005</t>
-  </si>
-  <si>
-    <t>0.9481,0.0228,0.0170,0.0004</t>
-  </si>
-  <si>
-    <t>0.4156,0.5846,0.1111,0.0016</t>
-  </si>
-  <si>
-    <t>0.9240,0.0409,0.0191,0.0014</t>
-  </si>
-  <si>
-    <t>0.9379,0.0280,0.0251,0.0005</t>
-  </si>
-  <si>
-    <t>0.6110,0.3522,0.0474,0.0088</t>
-  </si>
-  <si>
-    <t>0.8739,0.0763,0.0323,0.0024</t>
-  </si>
-  <si>
-    <t>0.5200,0.4605,0.0396,0.0077</t>
-  </si>
-  <si>
-    <t>0.7021,0.1377,0.0272,0.0157</t>
-  </si>
-  <si>
-    <t>0.7548,0.1682,0.0659,0.0065</t>
-  </si>
-  <si>
-    <t>0.9500,0.0066,0.0295,0.0006</t>
-  </si>
-  <si>
-    <t>0.9580,0.0133,0.0184,0.0004</t>
-  </si>
-  <si>
-    <t>0.9398,0.0151,0.0391,0.0005</t>
-  </si>
-  <si>
-    <t>0.9230,0.0162,0.0524,0.0003</t>
-  </si>
-  <si>
-    <t>0.8945,0.0412,0.0637,0.0008</t>
-  </si>
-  <si>
-    <t>0.8058,0.0211,0.2007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9656,0.0040,0.0296,0.0001</t>
-  </si>
-  <si>
-    <t>0.9391,0.0023,0.0859,0.0001</t>
-  </si>
-  <si>
-    <t>0.9692,0.0045,0.0125,0.0001</t>
-  </si>
-  <si>
-    <t>0.8386,0.0058,0.2504,0.0003</t>
-  </si>
-  <si>
-    <t>0.6074,0.3041,0.0564,0.0108</t>
-  </si>
-  <si>
-    <t>0.8799,0.0468,0.0190,0.0084</t>
-  </si>
-  <si>
-    <t>0.7997,0.0820,0.0276,0.0100</t>
-  </si>
-  <si>
-    <t>0.6104,0.1769,0.0603,0.0360</t>
-  </si>
-  <si>
-    <t>0.7212,0.0976,0.0947,0.0178</t>
-  </si>
-  <si>
-    <t>0.7136,0.0976,0.0948,0.0333</t>
-  </si>
-  <si>
-    <t>0.7618,0.0718,0.0365,0.0237</t>
-  </si>
-  <si>
-    <t>0.8081,0.0721,0.0410,0.0115</t>
-  </si>
-  <si>
-    <t>0.8530,0.0915,0.0562,0.0039</t>
-  </si>
-  <si>
-    <t>0.8976,0.0410,0.0264,0.0020</t>
-  </si>
-  <si>
-    <t>0.9058,0.0498,0.0325,0.0013</t>
-  </si>
-  <si>
-    <t>0.9065,0.0005,0.1863,0.0000</t>
-  </si>
-  <si>
-    <t>0.8390,0.0046,0.1591,0.0022</t>
-  </si>
-  <si>
-    <t>0.7503,0.0164,0.3391,0.0003</t>
-  </si>
-  <si>
-    <t>0.4820,0.0025,0.8007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9403,0.0040,0.0695,0.0002</t>
-  </si>
-  <si>
-    <t>0.6659,0.0040,0.4858,0.0005</t>
-  </si>
-  <si>
-    <t>0.9339,0.0036,0.0524,0.0001</t>
-  </si>
-  <si>
-    <t>0.9151,0.0346,0.0386,0.0003</t>
-  </si>
-  <si>
-    <t>0.9418,0.0259,0.0210,0.0005</t>
-  </si>
-  <si>
-    <t>0.9766,0.0044,0.0121,0.0001</t>
-  </si>
-  <si>
-    <t>0.9411,0.0170,0.0308,0.0005</t>
-  </si>
-  <si>
-    <t>0.7494,0.2446,0.0303,0.0053</t>
-  </si>
-  <si>
-    <t>0.7422,0.1675,0.0505,0.0077</t>
-  </si>
-  <si>
-    <t>0.8111,0.0429,0.0187,0.0246</t>
-  </si>
-  <si>
-    <t>0.6790,0.2096,0.0423,0.0116</t>
-  </si>
-  <si>
-    <t>0.7070,0.1078,0.0809,0.0378</t>
-  </si>
-  <si>
-    <t>0.7297,0.0949,0.1297,0.0183</t>
-  </si>
-  <si>
-    <t>0.7366,0.1372,0.0342,0.0138</t>
-  </si>
-  <si>
-    <t>0.8306,0.0634,0.0572,0.0084</t>
-  </si>
-  <si>
-    <t>0.7913,0.0388,0.1711,0.0002</t>
-  </si>
-  <si>
-    <t>0.5951,0.0149,0.6039,0.0002</t>
-  </si>
-  <si>
-    <t>0.9249,0.0048,0.0789,0.0002</t>
-  </si>
-  <si>
-    <t>0.9756,0.0032,0.0116,0.0003</t>
-  </si>
-  <si>
-    <t>0.9156,0.0073,0.1049,0.0001</t>
-  </si>
-  <si>
-    <t>0.9447,0.0076,0.0407,0.0006</t>
-  </si>
-  <si>
-    <t>0.9345,0.0176,0.0390,0.0003</t>
-  </si>
-  <si>
-    <t>0.9752,0.0011,0.0220,0.0001</t>
-  </si>
-  <si>
-    <t>0.7096,0.0889,0.0742,0.0352</t>
-  </si>
-  <si>
-    <t>0.9290,0.0371,0.0312,0.0007</t>
-  </si>
-  <si>
-    <t>0.8975,0.0408,0.0455,0.0034</t>
-  </si>
-  <si>
-    <t>0.9257,0.0186,0.0246,0.0032</t>
-  </si>
-  <si>
-    <t>0.7900,0.0414,0.0509,0.0407</t>
-  </si>
-  <si>
-    <t>0.7769,0.1480,0.0740,0.0031</t>
+    <t>0.9417,0.0288,0.0077,0.0186</t>
+  </si>
+  <si>
+    <t>0.0071,0.0003,0.0007,0.9968</t>
+  </si>
+  <si>
+    <t>0.9032,0.0028,0.0042,0.0836</t>
+  </si>
+  <si>
+    <t>0.2938,0.0116,0.0223,0.7652</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9961,0.0007,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9935,0.0004,0.0003,0.0045</t>
+  </si>
+  <si>
+    <t>0.9978,0.0002,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9948,0.0031,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9873,0.0049,0.0032,0.0021</t>
+  </si>
+  <si>
+    <t>0.9947,0.0014,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9974,0.0006,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9479,0.0361,0.0158,0.0011</t>
+  </si>
+  <si>
+    <t>0.1380,0.0243,0.8769,0.0010</t>
+  </si>
+  <si>
+    <t>0.2584,0.0118,0.8949,0.0012</t>
+  </si>
+  <si>
+    <t>0.0203,0.0031,0.9860,0.0026</t>
+  </si>
+  <si>
+    <t>0.6355,0.0050,0.3666,0.0077</t>
+  </si>
+  <si>
+    <t>0.0020,0.9950,0.0036,0.0007</t>
+  </si>
+  <si>
+    <t>0.0032,0.9924,0.0062,0.0016</t>
+  </si>
+  <si>
+    <t>0.0552,0.9388,0.0133,0.0026</t>
+  </si>
+  <si>
+    <t>0.0004,0.9979,0.0028,0.0016</t>
+  </si>
+  <si>
+    <t>0.0004,0.9985,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.6703,0.0065,0.3119,0.0304</t>
+  </si>
+  <si>
+    <t>0.5069,0.0094,0.2711,0.1342</t>
+  </si>
+  <si>
+    <t>0.0009,0.0006,0.9964,0.0033</t>
+  </si>
+  <si>
+    <t>0.2223,0.0010,0.8941,0.0020</t>
+  </si>
+  <si>
+    <t>0.0500,0.0013,0.9789,0.0014</t>
+  </si>
+  <si>
+    <t>0.0174,0.0015,0.9915,0.0016</t>
+  </si>
+  <si>
+    <t>0.0013,0.0022,0.9959,0.0048</t>
+  </si>
+  <si>
+    <t>0.6636,0.4187,0.0216,0.0047</t>
+  </si>
+  <si>
+    <t>0.2339,0.0973,0.7375,0.0160</t>
+  </si>
+  <si>
+    <t>0.0003,0.0020,0.9980,0.0037</t>
+  </si>
+  <si>
+    <t>0.0270,0.8938,0.0956,0.0007</t>
+  </si>
+  <si>
+    <t>0.5109,0.0408,0.5182,0.0412</t>
+  </si>
+  <si>
+    <t>0.9641,0.0114,0.0087,0.0064</t>
+  </si>
+  <si>
+    <t>0.9175,0.0960,0.0073,0.0027</t>
+  </si>
+  <si>
+    <t>0.0111,0.9709,0.4404,0.0013</t>
+  </si>
+  <si>
+    <t>0.0268,0.5249,0.7532,0.0468</t>
+  </si>
+  <si>
+    <t>0.0102,0.0044,0.9911,0.0015</t>
+  </si>
+  <si>
+    <t>0.0120,0.0039,0.9848,0.0058</t>
+  </si>
+  <si>
+    <t>0.4361,0.0010,0.5288,0.0085</t>
+  </si>
+  <si>
+    <t>0.0383,0.0480,0.9706,0.0029</t>
+  </si>
+  <si>
+    <t>0.0046,0.9837,0.0144,0.0039</t>
+  </si>
+  <si>
+    <t>0.0013,0.0064,0.9950,0.0022</t>
+  </si>
+  <si>
+    <t>0.0892,0.3408,0.0092,0.7985</t>
+  </si>
+  <si>
+    <t>0.0117,0.9664,0.0077,0.0286</t>
+  </si>
+  <si>
+    <t>0.0030,0.9916,0.0203,0.0006</t>
+  </si>
+  <si>
+    <t>0.0013,0.9943,0.0094,0.0014</t>
+  </si>
+  <si>
+    <t>0.0013,0.0871,0.9830,0.0047</t>
+  </si>
+  <si>
+    <t>0.0023,0.3573,0.9860,0.0012</t>
+  </si>
+  <si>
+    <t>0.3082,0.0044,0.8423,0.0030</t>
+  </si>
+  <si>
+    <t>0.0345,0.0020,0.9816,0.0030</t>
+  </si>
+  <si>
+    <t>0.0023,0.0026,0.9949,0.0020</t>
+  </si>
+  <si>
+    <t>0.0120,0.0021,0.9923,0.0012</t>
+  </si>
+  <si>
+    <t>0.9834,0.0154,0.0012,0.0014</t>
+  </si>
+  <si>
+    <t>0.9757,0.0066,0.0117,0.0019</t>
+  </si>
+  <si>
+    <t>0.9703,0.0048,0.0078,0.0096</t>
+  </si>
+  <si>
+    <t>0.0054,0.0274,0.9897,0.0063</t>
+  </si>
+  <si>
+    <t>0.9948,0.0014,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9822,0.0146,0.0017,0.0025</t>
+  </si>
+  <si>
+    <t>0.9868,0.0110,0.0010,0.0011</t>
+  </si>
+  <si>
+    <t>0.0034,0.8419,0.9611,0.0014</t>
+  </si>
+  <si>
+    <t>0.0021,0.0116,0.9955,0.0018</t>
+  </si>
+  <si>
+    <t>0.0650,0.0403,0.9173,0.0266</t>
+  </si>
+  <si>
+    <t>0.0009,0.9358,0.9706,0.0003</t>
+  </si>
+  <si>
+    <t>0.0081,0.0032,0.9914,0.0021</t>
+  </si>
+  <si>
+    <t>0.0175,0.9734,0.0062,0.0007</t>
+  </si>
+  <si>
+    <t>0.0116,0.9803,0.0116,0.0008</t>
+  </si>
+  <si>
+    <t>0.8369,0.0211,0.2014,0.0145</t>
+  </si>
+  <si>
+    <t>0.3318,0.0893,0.7577,0.0075</t>
+  </si>
+  <si>
+    <t>0.0023,0.0032,0.9953,0.0061</t>
+  </si>
+  <si>
+    <t>0.0021,0.9710,0.8025,0.0008</t>
+  </si>
+  <si>
+    <t>0.0091,0.9002,0.7455,0.0010</t>
+  </si>
+  <si>
+    <t>0.0554,0.8476,0.1101,0.0008</t>
+  </si>
+  <si>
+    <t>0.0024,0.8175,0.9331,0.0020</t>
+  </si>
+  <si>
+    <t>0.0185,0.0027,0.0622,0.9636</t>
+  </si>
+  <si>
+    <t>0.0006,0.0011,0.0002,0.9995</t>
+  </si>
+  <si>
+    <t>0.0011,0.0008,0.0003,0.9993</t>
+  </si>
+  <si>
+    <t>0.0078,0.0011,0.0050,0.9939</t>
+  </si>
+  <si>
+    <t>0.0010,0.0055,0.0020,0.9980</t>
+  </si>
+  <si>
+    <t>0.0035,0.0025,0.0013,0.9972</t>
+  </si>
+  <si>
+    <t>0.0017,0.9514,0.9028,0.0004</t>
+  </si>
+  <si>
+    <t>0.0062,0.5211,0.9642,0.0018</t>
+  </si>
+  <si>
+    <t>0.0158,0.8885,0.3642,0.0085</t>
+  </si>
+  <si>
+    <t>0.0036,0.9587,0.5365,0.0016</t>
+  </si>
+  <si>
+    <t>0.0010,0.8193,0.9737,0.0002</t>
+  </si>
+  <si>
+    <t>0.0022,0.9732,0.4383,0.0007</t>
+  </si>
+  <si>
+    <t>0.9964,0.0005,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9795,0.0166,0.0031,0.0024</t>
+  </si>
+  <si>
+    <t>0.9854,0.0089,0.0018,0.0020</t>
+  </si>
+  <si>
+    <t>0.9919,0.0029,0.0006,0.0019</t>
+  </si>
+  <si>
+    <t>0.9941,0.0063,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9940,0.0018,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9935,0.0031,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9895,0.0044,0.0025,0.0015</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9954,0.0010,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9967,0.0005,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9935,0.0020,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9953,0.0011,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9929,0.0021,0.0006,0.0017</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.0095,0.0019,0.9932,0.0008</t>
+  </si>
+  <si>
+    <t>0.0346,0.0016,0.9897,0.0006</t>
+  </si>
+  <si>
+    <t>0.9036,0.0068,0.0547,0.0133</t>
+  </si>
+  <si>
+    <t>0.0136,0.0011,0.9901,0.0033</t>
+  </si>
+  <si>
+    <t>0.0255,0.9644,0.0062,0.0020</t>
+  </si>
+  <si>
+    <t>0.0032,0.9912,0.0065,0.0021</t>
+  </si>
+  <si>
+    <t>0.0232,0.9630,0.0042,0.0059</t>
+  </si>
+  <si>
+    <t>0.0126,0.9761,0.0068,0.0050</t>
+  </si>
+  <si>
+    <t>0.0018,0.9946,0.0019,0.0020</t>
+  </si>
+  <si>
+    <t>0.0007,0.9962,0.0007,0.0036</t>
+  </si>
+  <si>
+    <t>0.9710,0.0528,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9163,0.0120,0.0626,0.0041</t>
+  </si>
+  <si>
+    <t>0.2674,0.0053,0.8662,0.0027</t>
+  </si>
+  <si>
+    <t>0.4730,0.0105,0.3574,0.1152</t>
+  </si>
+  <si>
+    <t>0.6255,0.0141,0.3690,0.0126</t>
+  </si>
+  <si>
+    <t>0.0430,0.0361,0.1383,0.8962</t>
+  </si>
+  <si>
+    <t>0.0064,0.9903,0.0096,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.9941,0.0028,0.0084</t>
+  </si>
+  <si>
+    <t>0.0009,0.9926,0.0036,0.0165</t>
+  </si>
+  <si>
+    <t>0.0022,0.9244,0.8944,0.0007</t>
+  </si>
+  <si>
+    <t>0.0113,0.9863,0.0191,0.0002</t>
+  </si>
+  <si>
+    <t>0.8014,0.1938,0.0734,0.0102</t>
+  </si>
+  <si>
+    <t>0.9143,0.0593,0.0253,0.0116</t>
+  </si>
+  <si>
+    <t>0.9939,0.0015,0.0010,0.0011</t>
+  </si>
+  <si>
+    <t>0.9986,0.0000,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9941,0.0010,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9832,0.0010,0.0108,0.0015</t>
+  </si>
+  <si>
+    <t>0.9952,0.0010,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9956,0.0013,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9970,0.0002,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9925,0.0002,0.0003,0.0052</t>
+  </si>
+  <si>
+    <t>0.0023,0.4005,0.9701,0.0007</t>
+  </si>
+  <si>
+    <t>0.0121,0.2807,0.9448,0.0009</t>
+  </si>
+  <si>
+    <t>0.0091,0.1340,0.9800,0.0006</t>
+  </si>
+  <si>
+    <t>0.0121,0.2715,0.9365,0.0034</t>
+  </si>
+  <si>
+    <t>0.9851,0.0039,0.0038,0.0006</t>
+  </si>
+  <si>
+    <t>0.9256,0.0031,0.0506,0.0060</t>
+  </si>
+  <si>
+    <t>0.2240,0.0020,0.8974,0.0042</t>
+  </si>
+  <si>
+    <t>0.6236,0.0187,0.5013,0.0017</t>
+  </si>
+  <si>
+    <t>0.1087,0.0011,0.0027,0.9552</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0004,0.9998</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0007,0.9996</t>
+  </si>
+  <si>
+    <t>0.0015,0.0002,0.0012,0.9986</t>
+  </si>
+  <si>
+    <t>0.0028,0.8110,0.8763,0.0059</t>
+  </si>
+  <si>
+    <t>0.9860,0.0023,0.0034,0.0036</t>
+  </si>
+  <si>
+    <t>0.0316,0.9571,0.0024,0.0142</t>
+  </si>
+  <si>
+    <t>0.9757,0.0060,0.0040,0.0107</t>
+  </si>
+  <si>
+    <t>0.2675,0.7978,0.0105,0.0086</t>
+  </si>
+  <si>
+    <t>0.9948,0.0007,0.0004,0.0020</t>
+  </si>
+  <si>
+    <t>0.6625,0.0098,0.0705,0.2281</t>
+  </si>
+  <si>
+    <t>0.9824,0.0023,0.0016,0.0071</t>
+  </si>
+  <si>
+    <t>0.0025,0.1410,0.9738,0.0222</t>
+  </si>
+  <si>
+    <t>0.3493,0.0004,0.0009,0.8344</t>
+  </si>
+  <si>
+    <t>0.7226,0.0034,0.0055,0.3496</t>
+  </si>
+  <si>
+    <t>0.5785,0.1814,0.2353,0.0210</t>
+  </si>
+  <si>
+    <t>0.9350,0.0151,0.0256,0.0222</t>
+  </si>
+  <si>
+    <t>0.9927,0.0029,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.1456,0.8033,0.0943,0.0217</t>
+  </si>
+  <si>
+    <t>0.9897,0.0038,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.9877,0.0123,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.9863,0.0011,0.0034,0.0038</t>
+  </si>
+  <si>
+    <t>0.9862,0.0055,0.0027,0.0026</t>
+  </si>
+  <si>
+    <t>0.9925,0.0004,0.0008,0.0028</t>
+  </si>
+  <si>
+    <t>0.9932,0.0001,0.0006,0.0032</t>
+  </si>
+  <si>
+    <t>0.9957,0.0007,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9873,0.0038,0.0025,0.0021</t>
+  </si>
+  <si>
+    <t>0.9921,0.0020,0.0007,0.0023</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9250,0.0348,0.0053,0.0130</t>
+  </si>
+  <si>
+    <t>0.8198,0.2482,0.0069,0.0015</t>
+  </si>
+  <si>
+    <t>0.6564,0.4019,0.0180,0.0038</t>
+  </si>
+  <si>
+    <t>0.6024,0.1167,0.3824,0.0123</t>
+  </si>
+  <si>
+    <t>0.9968,0.0007,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9838,0.0085,0.0028,0.0017</t>
+  </si>
+  <si>
+    <t>0.9768,0.0190,0.0024,0.0031</t>
+  </si>
+  <si>
+    <t>0.9795,0.0038,0.0006,0.0098</t>
+  </si>
+  <si>
+    <t>0.0013,0.0052,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.9047,0.0781,0.0286,0.0127</t>
+  </si>
+  <si>
+    <t>0.0069,0.0027,0.9940,0.0009</t>
+  </si>
+  <si>
+    <t>0.0082,0.0079,0.9903,0.0029</t>
+  </si>
+  <si>
+    <t>0.0042,0.0020,0.9965,0.0010</t>
+  </si>
+  <si>
+    <t>0.0055,0.0281,0.9856,0.0049</t>
+  </si>
+  <si>
+    <t>0.0103,0.0016,0.9947,0.0005</t>
+  </si>
+  <si>
+    <t>0.0061,0.0013,0.9955,0.0009</t>
+  </si>
+  <si>
+    <t>0.0009,0.0008,0.9987,0.0003</t>
+  </si>
+  <si>
+    <t>0.0823,0.0041,0.9465,0.0097</t>
+  </si>
+  <si>
+    <t>0.1332,0.0044,0.9285,0.0067</t>
+  </si>
+  <si>
+    <t>0.2349,0.0063,0.9018,0.0011</t>
+  </si>
+  <si>
+    <t>0.2033,0.1652,0.6504,0.0088</t>
+  </si>
+  <si>
+    <t>0.2181,0.0682,0.7415,0.0140</t>
+  </si>
+  <si>
+    <t>0.9298,0.0039,0.0648,0.0006</t>
+  </si>
+  <si>
+    <t>0.5537,0.0590,0.4300,0.0401</t>
+  </si>
+  <si>
+    <t>0.0708,0.0073,0.9444,0.0137</t>
+  </si>
+  <si>
+    <t>0.4907,0.6480,0.0036,0.0029</t>
+  </si>
+  <si>
+    <t>0.0130,0.9857,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.8484,0.1919,0.0195,0.0048</t>
+  </si>
+  <si>
+    <t>0.9680,0.0338,0.0010,0.0022</t>
+  </si>
+  <si>
+    <t>0.6493,0.4425,0.0022,0.0050</t>
+  </si>
+  <si>
+    <t>0.8350,0.0131,0.1656,0.0059</t>
+  </si>
+  <si>
+    <t>0.9642,0.0013,0.0302,0.0009</t>
+  </si>
+  <si>
+    <t>0.5737,0.0055,0.0261,0.3926</t>
+  </si>
+  <si>
+    <t>0.9073,0.0010,0.1897,0.0001</t>
+  </si>
+  <si>
+    <t>0.8961,0.0054,0.0829,0.0038</t>
+  </si>
+  <si>
+    <t>0.0098,0.0075,0.9815,0.0092</t>
+  </si>
+  <si>
+    <t>0.0107,0.0106,0.9728,0.0102</t>
+  </si>
+  <si>
+    <t>0.0629,0.0062,0.9541,0.0072</t>
+  </si>
+  <si>
+    <t>0.0090,0.0087,0.9873,0.0027</t>
+  </si>
+  <si>
+    <t>0.0163,0.0612,0.9518,0.0052</t>
+  </si>
+  <si>
+    <t>0.9935,0.0011,0.0004,0.0021</t>
+  </si>
+  <si>
+    <t>0.9947,0.0011,0.0004,0.0016</t>
+  </si>
+  <si>
+    <t>0.9870,0.0074,0.0006,0.0019</t>
+  </si>
+  <si>
+    <t>0.9875,0.0082,0.0024,0.0015</t>
+  </si>
+  <si>
+    <t>0.9904,0.0022,0.0008,0.0032</t>
+  </si>
+  <si>
+    <t>0.9928,0.0038,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9960,0.0008,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9951,0.0008,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.2398,0.0031,0.9250,0.0009</t>
+  </si>
+  <si>
+    <t>0.1647,0.7712,0.3376,0.0315</t>
+  </si>
+  <si>
+    <t>0.9296,0.0244,0.0360,0.0076</t>
+  </si>
+  <si>
+    <t>0.0284,0.0031,0.9852,0.0011</t>
+  </si>
+  <si>
+    <t>0.0006,0.0006,0.9960,0.0088</t>
+  </si>
+  <si>
+    <t>0.0046,0.0452,0.9808,0.0070</t>
+  </si>
+  <si>
+    <t>0.0051,0.0016,0.9955,0.0009</t>
+  </si>
+  <si>
+    <t>0.0834,0.0097,0.9391,0.0029</t>
+  </si>
+  <si>
+    <t>0.0004,0.0019,0.9988,0.0006</t>
+  </si>
+  <si>
+    <t>0.0025,0.0022,0.9880,0.0174</t>
+  </si>
+  <si>
+    <t>0.0308,0.0421,0.8906,0.1150</t>
+  </si>
+  <si>
+    <t>0.9028,0.0010,0.0829,0.0050</t>
+  </si>
+  <si>
+    <t>0.9507,0.0025,0.0366,0.0018</t>
+  </si>
+  <si>
+    <t>0.9248,0.0143,0.0087,0.0326</t>
+  </si>
+  <si>
+    <t>0.9908,0.0050,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9918,0.0021,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.9976,0.0010,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9925,0.0042,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.9968,0.0005,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9974,0.0004,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9934,0.0043,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9959,0.0016,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.0058,0.0066,0.9881,0.0042</t>
+  </si>
+  <si>
+    <t>0.0025,0.4896,0.9790,0.0006</t>
+  </si>
+  <si>
+    <t>0.0054,0.0066,0.9926,0.0023</t>
+  </si>
+  <si>
+    <t>0.1498,0.0018,0.9443,0.0002</t>
+  </si>
+  <si>
+    <t>0.0051,0.0040,0.9954,0.0005</t>
+  </si>
+  <si>
+    <t>0.9288,0.0015,0.0609,0.0036</t>
+  </si>
+  <si>
+    <t>0.0228,0.0025,0.9909,0.0008</t>
+  </si>
+  <si>
+    <t>0.0734,0.0082,0.9049,0.0297</t>
+  </si>
+  <si>
+    <t>0.9359,0.0004,0.0046,0.0357</t>
+  </si>
+  <si>
+    <t>0.0079,0.0071,0.0008,0.9947</t>
+  </si>
+  <si>
+    <t>0.0223,0.0005,0.0014,0.9909</t>
+  </si>
+  <si>
+    <t>0.0012,0.0003,0.0016,0.9986</t>
+  </si>
+  <si>
+    <t>0.0023,0.0001,0.0002,0.9991</t>
+  </si>
+  <si>
+    <t>0.9153,0.0030,0.0054,0.0581</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2415,7 +2415,7 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D35" t="s">
         <v>297</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2737,7 +2737,7 @@
         <v>259</v>
       </c>
       <c r="C58" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D58" t="s">
         <v>320</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3927,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
         <v>405</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4123,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
         <v>419</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
         <v>457</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5131,7 +5131,7 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D229" t="s">
         <v>491</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
